--- a/交通觀光景點分析 + 鄉鎮際搭乘分析/datasets/112-114/112-114年花蓮縣平假日分析.xlsx
+++ b/交通觀光景點分析 + 鄉鎮際搭乘分析/datasets/112-114/112-114年花蓮縣平假日分析.xlsx
@@ -1,114 +1,128 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\115_Midterm-Report\交通觀光景點分析 + 鄉鎮際搭乘分析\datasets\112-114\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_E63E522444B1EB299176987C0D3E1B9392597480" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="112-114年花蓮縣平假日分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="112-114年花蓮縣平假日分析" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
-    <t xml:space="preserve">景點</t>
-  </si>
-  <si>
-    <t xml:space="preserve">平日</t>
-  </si>
-  <si>
-    <t xml:space="preserve">假日</t>
-  </si>
-  <si>
-    <t xml:space="preserve">平日平均</t>
-  </si>
-  <si>
-    <t xml:space="preserve">假日平均</t>
-  </si>
-  <si>
-    <t xml:space="preserve">平假日平均比值百分比</t>
-  </si>
-  <si>
-    <t xml:space="preserve">太魯閣</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.04%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">志學車站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.41%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">新城車站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.88%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">新天堂樂園</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.23%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">東大門夜市</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.79%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海洋公園</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.98%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">玉里車站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.71%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">瑞穗車站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.01%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">花蓮航空站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.65%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">花蓮轉運站/車站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.94%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">總計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.77%</t>
+    <t>景點</t>
+  </si>
+  <si>
+    <t>平日</t>
+  </si>
+  <si>
+    <t>假日</t>
+  </si>
+  <si>
+    <t>平日平均</t>
+  </si>
+  <si>
+    <t>假日平均</t>
+  </si>
+  <si>
+    <t>平假日平均比值百分比</t>
+  </si>
+  <si>
+    <t>太魯閣</t>
+  </si>
+  <si>
+    <t>82.04%</t>
+  </si>
+  <si>
+    <t>志學車站</t>
+  </si>
+  <si>
+    <t>117.41%</t>
+  </si>
+  <si>
+    <t>新城車站</t>
+  </si>
+  <si>
+    <t>76.88%</t>
+  </si>
+  <si>
+    <t>新天堂樂園</t>
+  </si>
+  <si>
+    <t>79.23%</t>
+  </si>
+  <si>
+    <t>東大門夜市</t>
+  </si>
+  <si>
+    <t>90.79%</t>
+  </si>
+  <si>
+    <t>海洋公園</t>
+  </si>
+  <si>
+    <t>51.98%</t>
+  </si>
+  <si>
+    <t>玉里車站</t>
+  </si>
+  <si>
+    <t>117.71%</t>
+  </si>
+  <si>
+    <t>瑞穗車站</t>
+  </si>
+  <si>
+    <t>154.01%</t>
+  </si>
+  <si>
+    <t>花蓮航空站</t>
+  </si>
+  <si>
+    <t>40.65%</t>
+  </si>
+  <si>
+    <t>花蓮轉運站/車站</t>
+  </si>
+  <si>
+    <t>95.94%</t>
+  </si>
+  <si>
+    <t>總計</t>
+  </si>
+  <si>
+    <t>91.77%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -136,9 +150,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,11 +443,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -444,228 +467,229 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>42863</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>20885</v>
       </c>
-      <c r="D2" t="n">
-        <v>54.7420178799489</v>
-      </c>
-      <c r="E2" t="n">
-        <v>66.7252396166134</v>
+      <c r="D2">
+        <v>54.742017879948897</v>
+      </c>
+      <c r="E2">
+        <v>66.725239616613393</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>7055</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>2402</v>
       </c>
-      <c r="D3" t="n">
-        <v>9.01021711366539</v>
-      </c>
-      <c r="E3" t="n">
-        <v>7.6741214057508</v>
+      <c r="D3">
+        <v>9.0102171136653908</v>
+      </c>
+      <c r="E3">
+        <v>7.6741214057507996</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>30207</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>15707</v>
       </c>
-      <c r="D4" t="n">
-        <v>38.5785440613027</v>
-      </c>
-      <c r="E4" t="n">
-        <v>50.1821086261981</v>
+      <c r="D4">
+        <v>38.578544061302701</v>
+      </c>
+      <c r="E4">
+        <v>50.182108626198101</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>10070</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>5081</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>12.8607918263091</v>
       </c>
-      <c r="E5" t="n">
-        <v>16.2332268370607</v>
+      <c r="E5">
+        <v>16.233226837060698</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>128194</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>56441</v>
       </c>
-      <c r="D6" t="n">
-        <v>163.721583652618</v>
-      </c>
-      <c r="E6" t="n">
-        <v>180.32268370607</v>
+      <c r="D6">
+        <v>163.72158365261799</v>
+      </c>
+      <c r="E6">
+        <v>180.32268370606999</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>12757</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>9810</v>
       </c>
-      <c r="D7" t="n">
-        <v>16.2924648786718</v>
-      </c>
-      <c r="E7" t="n">
-        <v>31.3418530351438</v>
+      <c r="D7">
+        <v>16.292464878671801</v>
+      </c>
+      <c r="E7">
+        <v>31.341853035143799</v>
       </c>
       <c r="F7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>41560</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>14114</v>
       </c>
-      <c r="D8" t="n">
-        <v>53.0779054916986</v>
-      </c>
-      <c r="E8" t="n">
-        <v>45.0926517571885</v>
+      <c r="D8">
+        <v>53.077905491698601</v>
+      </c>
+      <c r="E8">
+        <v>45.092651757188499</v>
       </c>
       <c r="F8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>12876</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>3342</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>16.4444444444444</v>
       </c>
-      <c r="E9" t="n">
-        <v>10.6773162939297</v>
+      <c r="E9">
+        <v>10.677316293929699</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>848</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>834</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>1.08301404853129</v>
       </c>
-      <c r="E10" t="n">
-        <v>2.66453674121406</v>
+      <c r="E10">
+        <v>2.6645367412140599</v>
       </c>
       <c r="F10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>203663</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>84858</v>
       </c>
-      <c r="D11" t="n">
-        <v>260.106002554278</v>
-      </c>
-      <c r="E11" t="n">
-        <v>271.111821086262</v>
+      <c r="D11">
+        <v>260.10600255427801</v>
+      </c>
+      <c r="E11">
+        <v>271.11182108626201</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>26</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>490093</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>213474</v>
       </c>
-      <c r="D12" t="n">
-        <v>625.916985951469</v>
-      </c>
-      <c r="E12" t="n">
-        <v>682.025559105431</v>
+      <c r="D12">
+        <v>625.91698595146897</v>
+      </c>
+      <c r="E12">
+        <v>682.02555910543094</v>
       </c>
       <c r="F12" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>